--- a/Datasets/sample.xlsx
+++ b/Datasets/sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Navigate lab\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94734000-5A8E-4375-BB45-ED920D31DE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10929775-7739-4C33-B880-CF34851C99E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB03280B-C001-4165-81B3-62DD5CFB438A}"/>
   </bookViews>
@@ -34,25 +34,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>weight</t>
+    <t>Carat</t>
   </si>
   <si>
-    <t>price</t>
+    <t>Cut_Score</t>
+  </si>
+  <si>
+    <t>Color_Score</t>
+  </si>
+  <si>
+    <t>Clarity_Score</t>
+  </si>
+  <si>
+    <t>Price_USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,8 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,63 +407,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523567EE-02B9-4D74-8751-7DACE83CEF5D}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="D2" s="1">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="D3" s="1">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="D4" s="1">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>77000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>99000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>110000</v>
+      <c r="E10" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7000</v>
       </c>
     </row>
   </sheetData>
